--- a/filer/32788718_flugger.xlsx
+++ b/filer/32788718_flugger.xlsx
@@ -5709,8 +5709,12 @@
       </c>
       <c r="B50" s="16" t="n"/>
       <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
+      <c r="D50" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>20</v>
+      </c>
       <c r="F50" s="16" t="n"/>
     </row>
     <row r="51">
@@ -6989,7 +6993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7298,21 +7302,25 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentAccrualsAndCurrentDeferredIncomeIncludingCurrentContractLiabilities</t>
+          <t>ifrs-full:CurrentInvestments</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentAccrualsAndCurrentDeferredIncomeIncludingCurrentContractLiabilities</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
+          <t>ifrs-full:CurrentInvestments</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>63</v>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>62</v>
+      </c>
       <c r="F10" s="38" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
@@ -7329,25 +7337,25 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentInvestments</t>
+          <t>ifrs-full:ImpairmentLossReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentInvestments</t>
+          <t>ifrs-full:ImpairmentLossReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>62</v>
+        <v>73726</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>56</v>
+        <v>-4188</v>
       </c>
       <c r="G11" s="35" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
@@ -7364,27 +7372,29 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:ImpairmentLossReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
+          <t>ifrs-full:IncomeFromContinuingOperationsAttributableToOwnersOfParent</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:ImpairmentLossReversalOfImpairmentLossRecognisedInProfitOrLoss</t>
+          <t>ifrs-full:IncomeFromContinuingOperationsAttributableToOwnersOfParent</t>
         </is>
       </c>
       <c r="D12" s="38" t="n">
-        <v>0</v>
+        <v>170837</v>
       </c>
       <c r="E12" s="38" t="n">
-        <v>73726</v>
+        <v>52921</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>-4188</v>
+        <v>-20146</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="38" t="n"/>
+        <v>18632</v>
+      </c>
+      <c r="H12" s="38" t="n">
+        <v>58000</v>
+      </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7399,29 +7409,21 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeFromContinuingOperationsAttributableToOwnersOfParent</t>
+          <t>ifrs-full:ReclassificationAdjustmentsOnExchangeDifferencesOnTranslationBeforeTax</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncomeFromContinuingOperationsAttributableToOwnersOfParent</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>170837</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>52921</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>-20146</v>
-      </c>
+          <t>ifrs-full:ReclassificationAdjustmentsOnExchangeDifferencesOnTranslationBeforeTax</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
       <c r="G13" s="35" t="n">
-        <v>18632</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>58000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7436,19 +7438,29 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:MiscellaneousOtherOperatingExpense</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:MiscellaneousOtherOperatingExpense</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n">
+        <v>-93493</v>
+      </c>
+      <c r="E14" s="38" t="n">
+        <v>-93493</v>
+      </c>
+      <c r="F14" s="38" t="n">
+        <v>-156176</v>
+      </c>
+      <c r="G14" s="38" t="n">
+        <v>-146633</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>-110000</v>
+      </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7463,12 +7475,12 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:MiscellaneousOtherOperatingIncome</t>
+          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:MiscellaneousOtherOperatingIncome</t>
+          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
         </is>
       </c>
       <c r="D15" s="35" t="n"/>
@@ -7482,204 +7494,6 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n">
-        <v>28279</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromDisposalsOfPropertyPlantAndEquipmentIntangibleAssetsOtherThanGoodwillInvestmentPropertyAndOtherNoncurrentAssets</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromDisposalsOfPropertyPlantAndEquipmentIntangibleAssetsOtherThanGoodwillInvestmentPropertyAndOtherNoncurrentAssets</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>2922</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>18111</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>1258</v>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>1087</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProfitLossFromContinuingOperationsAttributableToNoncontrollingInterests</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProfitLossFromContinuingOperationsAttributableToNoncontrollingInterests</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>9144</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>-9879</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>11552</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>6636</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReclassificationAdjustmentsOnExchangeDifferencesOnTranslationBeforeTax</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReclassificationAdjustmentsOnExchangeDifferencesOnTranslationBeforeTax</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n">
-        <v>-93493</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>-93493</v>
-      </c>
-      <c r="F20" s="38" t="n">
-        <v>-156176</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>-146633</v>
-      </c>
-      <c r="H20" s="38" t="n">
-        <v>-110000</v>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RestrictedCashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filer/32788718_flugger.xlsx
+++ b/filer/32788718_flugger.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4434,6 +4435,148 @@
       </c>
       <c r="F91" s="13">
         <f>IFERROR($F$31/($F$53+$F$60)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B98">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4482,346 +4625,346 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>2161640</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>2321548</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>2130156</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>2208344</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>2272000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>946793</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>1112170</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>1102425</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>1073261</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>1055000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>1214847</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>1209378</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>1027731</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>1135083</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>1217000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>807786</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>851496</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>859672</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>871546</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>915000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>184583</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>195090</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>183690</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>197758</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>209000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>6719</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>15775</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>6089</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>6147</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>1077</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>5518</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>2258</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>3974</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>228120</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>99323</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>-7612</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>67952</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>94000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>19242</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>28525</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>39620</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>20996</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>27173</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>48449</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>48753</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>42623</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>34000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>220189</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>79399</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>-16745</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>46325</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>82000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>40208</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>36357</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-8151</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>21057</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>179981</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>43042</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>-8594</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>25268</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>63000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>120693</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>185904</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>72468</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>53845</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>40000</v>
       </c>
     </row>
@@ -4870,916 +5013,916 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>42933</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>88376</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>30975</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>28929</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>23000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>119329</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>159020</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>145122</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>147099</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>149000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>175270</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>272792</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>240723</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>227575</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>217000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>161275</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>250518</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>296843</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>272551</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>76626</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>103993</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>94327</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>135939</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>115659</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>135820</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>108640</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>24633</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>23000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>23941</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>70704</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>85000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>81790</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>91000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>973064</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>1219724</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1193815</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1087709</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>1089000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>344048</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>462082</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>468557</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>362131</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>375000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>368550</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>384186</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>451735</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>470825</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>432000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>13280</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>12807</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>39547</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>23656</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>156682</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>28748</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>17674</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>18084</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>24000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>869343</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>1005785</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>938022</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>851094</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>831000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>1842407</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>2225509</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>2131837</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>1938803</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <v>1920000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>60000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>-213</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>899788</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>910939</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>776121</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>820674</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>815000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>950890</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>918945</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>773591</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>820766</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>870000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>9309</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>22990</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>28957</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>27143</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>21000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>9309</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>22990</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>28957</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>27143</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>21000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>307195</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>298540</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>250879</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>264450</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>284000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>112710</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>112710</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>112710</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>104000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>321753</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>450240</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>453788</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>410329</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>418000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n">
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>78866</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>85739</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>88368</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>69658</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>87000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>219797</v>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>259121</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>252660</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>191689</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="17" t="n">
         <v>206000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>215516</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>168756</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>162979</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>162294</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>170000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n">
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="F50" s="16" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>569764</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>856324</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>904458</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>707708</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>632000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>891517</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>1306564</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>1358246</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>1118037</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="F52" s="17" t="n">
         <v>1050000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>1842407</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>2225509</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>2131837</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>1938803</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="17" t="n">
         <v>1920000</v>
       </c>
     </row>
@@ -5789,6 +5932,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>313069</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>96761</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>88473</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>194178</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>256000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-164802</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-264585</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-84083</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-66410</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-128580</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>38794</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-23479</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-129719</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-237000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6987,7 +7252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
